--- a/data/202603_멀티캠퍼스_매출 정산 변환.xlsx
+++ b/data/202603_멀티캠퍼스_매출 정산 변환.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\minion\Desktop\알라딘\알라딘아카데미 정산관련\26.03\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DDA63A9-3EC6-4193-BE3D-C8D74C80DC1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89940BCD-13D9-4E14-9CEF-D1C6F38DE1EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-29100" yWindow="2430" windowWidth="25350" windowHeight="18390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-26775" yWindow="1305" windowWidth="25350" windowHeight="18390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="매출 입력" sheetId="1" r:id="rId1"/>
@@ -137,24 +137,7 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0051A2"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>김광석</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0051A2"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>1</t>
-    </r>
+    <t>김광석</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -162,7 +145,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -209,13 +192,6 @@
       <sz val="10"/>
       <color rgb="FF0051A2"/>
       <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF0051A2"/>
-      <name val="Arial"/>
       <family val="3"/>
       <charset val="129"/>
     </font>
@@ -298,7 +274,7 @@
     <xf numFmtId="17" fontId="6" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
